--- a/Aspirant1Sem/НИР/Результаты работы/Результаты работы.xlsx
+++ b/Aspirant1Sem/НИР/Результаты работы/Результаты работы.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vitaly.gusev\Desktop\Универ\Bachelor_course\Aspirant1Sem\НИР\Результаты работы\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3A35602-4317-41B2-A6E2-5BFD032D7014}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C08B720-4333-44DA-81B1-4AE9EC3B35D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="14020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="97">
   <si>
     <t>N \ D</t>
   </si>
@@ -72,18 +72,6 @@
     <t>D</t>
   </si>
   <si>
-    <t>Сумма</t>
-  </si>
-  <si>
-    <t>Среднее</t>
-  </si>
-  <si>
-    <t>С нарастающим итогом</t>
-  </si>
-  <si>
-    <t>Количество</t>
-  </si>
-  <si>
     <t>Конфигурация</t>
   </si>
   <si>
@@ -107,12 +95,237 @@
   <si>
     <t>N=4, gamma, D=8, F=2</t>
   </si>
+  <si>
+    <t>Отчёт 3</t>
+  </si>
+  <si>
+    <t>Энтропия</t>
+  </si>
+  <si>
+    <t>MI(lag=1)</t>
+  </si>
+  <si>
+    <t>MI(lag=2)</t>
+  </si>
+  <si>
+    <t>p_дл_серий</t>
+  </si>
+  <si>
+    <t>Блочный (блок=3)</t>
+  </si>
+  <si>
+    <t>Gap (символ 0)</t>
+  </si>
+  <si>
+    <t>Линейная сложность</t>
+  </si>
+  <si>
+    <t>Вывод</t>
+  </si>
+  <si>
+    <t>Отличная случайность</t>
+  </si>
+  <si>
+    <t>Непригоден (периодическая структура)</t>
+  </si>
+  <si>
+    <t>–0,5000</t>
+  </si>
+  <si>
+    <t>Пункт 7,3</t>
+  </si>
+  <si>
+    <t>Пункт 7,4</t>
+  </si>
+  <si>
+    <t>Сильная зависимость</t>
+  </si>
+  <si>
+    <t>Оптимальный компромисс</t>
+  </si>
+  <si>
+    <t>N=3, exp, D=8</t>
+  </si>
+  <si>
+    <t>✅ отлично</t>
+  </si>
+  <si>
+    <t>❌ нарушение равномерности</t>
+  </si>
+  <si>
+    <t>N=4, gamma, D=8</t>
+  </si>
+  <si>
+    <t>Пункт 7,5</t>
+  </si>
+  <si>
+    <t>Пункт 7,6</t>
+  </si>
+  <si>
+    <t>Пункт 7,7</t>
+  </si>
+  <si>
+    <t>Выход</t>
+  </si>
+  <si>
+    <t>✅</t>
+  </si>
+  <si>
+    <t>Топология</t>
+  </si>
+  <si>
+    <t>ring</t>
+  </si>
+  <si>
+    <t>ring_omit_output</t>
+  </si>
+  <si>
+    <t>parallel_single</t>
+  </si>
+  <si>
+    <t>Пункт 7,8</t>
+  </si>
+  <si>
+    <t>Хорошая случайность</t>
+  </si>
+  <si>
+    <t>–0,0004</t>
+  </si>
+  <si>
+    <t>–0,0042</t>
+  </si>
+  <si>
+    <t>–0,0041</t>
+  </si>
+  <si>
+    <t>Приемлемая случайность (p_бигр.=0,0964 &gt; 0,05)</t>
+  </si>
+  <si>
+    <t>–0,0078</t>
+  </si>
+  <si>
+    <t>–0,0025</t>
+  </si>
+  <si>
+    <t>Наилучшие показатели</t>
+  </si>
+  <si>
+    <t>Хорошие, но чуть хуже по равномерности</t>
+  </si>
+  <si>
+    <t>–0,0030</t>
+  </si>
+  <si>
+    <t>Приемлемая случайность, но требует трёх независимых элементов</t>
+  </si>
+  <si>
+    <t>Сильная зависимость, непригоден</t>
+  </si>
+  <si>
+    <t>–0,0126</t>
+  </si>
+  <si>
+    <t>Зависимость ещё заметна (p_бигр., p_сер., p_дл_серий &lt; 0,05)</t>
+  </si>
+  <si>
+    <t>Независимость, но p_сер. и p_дл_серий на грани; скорость ниже</t>
+  </si>
+  <si>
+    <t>Метрика</t>
+  </si>
+  <si>
+    <t>Энтропия, бит/трит</t>
+  </si>
+  <si>
+    <t>Отлично</t>
+  </si>
+  <si>
+    <t>Непригоден</t>
+  </si>
+  <si>
+    <t>D=2</t>
+  </si>
+  <si>
+    <t>D=4</t>
+  </si>
+  <si>
+    <t>D=8</t>
+  </si>
+  <si>
+    <t>D=16</t>
+  </si>
+  <si>
+    <t>Зависимость заметна</t>
+  </si>
+  <si>
+    <t>Оптимальный</t>
+  </si>
+  <si>
+    <t>Независимость, но медленнее</t>
+  </si>
+  <si>
+    <t>N=1</t>
+  </si>
+  <si>
+    <t>N=2</t>
+  </si>
+  <si>
+    <t>N=3</t>
+  </si>
+  <si>
+    <t>N=4</t>
+  </si>
+  <si>
+    <t>N=5</t>
+  </si>
+  <si>
+    <t>N=6</t>
+  </si>
+  <si>
+    <t>Хорошо</t>
+  </si>
+  <si>
+    <t>Приемлемо</t>
+  </si>
+  <si>
+    <t>N=3, exp, F1</t>
+  </si>
+  <si>
+    <t>N=3, exp, F2</t>
+  </si>
+  <si>
+    <t>N=4, gamma, F1</t>
+  </si>
+  <si>
+    <t>N=4, gamma, F2</t>
+  </si>
+  <si>
+    <t>❌ негодна</t>
+  </si>
+  <si>
+    <t>output 0</t>
+  </si>
+  <si>
+    <t>output 1</t>
+  </si>
+  <si>
+    <t>output 2</t>
+  </si>
+  <si>
+    <t>Наилучший</t>
+  </si>
+  <si>
+    <t>Хороший</t>
+  </si>
+  <si>
+    <t>Приемлемый</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -151,8 +364,29 @@
       <family val="1"/>
       <charset val="204"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF0F1115"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF0F1115"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF0F1115"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -165,8 +399,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -226,11 +466,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -252,8 +507,26 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="11" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="17" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -918,16 +1191,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>0.4728</c:v>
+                  <c:v>0.2233</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.31559999999999999</c:v>
+                  <c:v>0.60909999999999997</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.25230000000000002</c:v>
+                  <c:v>0.95209999999999995</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2.5999999999999999E-3</c:v>
+                  <c:v>2.5000000000000001E-3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -989,16 +1262,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>0.19059999999999999</c:v>
+                  <c:v>0.88470000000000004</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.2429</c:v>
+                  <c:v>0.85009999999999997</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3.6299999999999999E-2</c:v>
+                  <c:v>0.76390000000000002</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>9.5999999999999992E-3</c:v>
+                  <c:v>4.0000000000000002E-4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1060,16 +1333,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>9.1700000000000004E-2</c:v>
+                  <c:v>0.70409999999999995</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.76339999999999997</c:v>
+                  <c:v>0.59050000000000002</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.3493</c:v>
+                  <c:v>0.51070000000000004</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2.5999999999999999E-3</c:v>
+                  <c:v>2.5000000000000001E-3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1411,7 +1684,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>0.50170000000000003</c:v>
+                  <c:v>0.69269999999999998</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
@@ -1420,7 +1693,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4.4299999999999999E-2</c:v>
+                  <c:v>4.6100000000000002E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1474,16 +1747,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>0.40229999999999999</c:v>
+                  <c:v>0.82230000000000003</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.0800000000000001E-2</c:v>
+                  <c:v>6.9999999999999999E-4</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4.7000000000000002E-3</c:v>
+                  <c:v>4.0000000000000001E-3</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-6.1999999999999998E-3</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1537,16 +1810,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>0.75160000000000005</c:v>
+                  <c:v>0.2233</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.69920000000000004</c:v>
+                  <c:v>0.60909999999999997</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.46899999999999997</c:v>
+                  <c:v>0.95209999999999995</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-5.8999999999999999E-3</c:v>
+                  <c:v>2.5000000000000001E-3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1600,16 +1873,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>0.34970000000000001</c:v>
+                  <c:v>0.48359999999999997</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.96120000000000005</c:v>
+                  <c:v>0.18559999999999999</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.92190000000000005</c:v>
+                  <c:v>5.57E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.2999999999999999E-3</c:v>
+                  <c:v>5.0000000000000001E-3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1880,16 +2153,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>0.97150000000000003</c:v>
+                  <c:v>0.61929999999999996</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.54900000000000004</c:v>
+                  <c:v>0.76839999999999997</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.2198</c:v>
+                  <c:v>0.44409999999999999</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-5.7999999999999996E-3</c:v>
+                  <c:v>6.9999999999999999E-4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1943,16 +2216,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>0.25800000000000001</c:v>
+                  <c:v>0.88770000000000004</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.63759999999999994</c:v>
+                  <c:v>0.70789999999999997</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.54169999999999996</c:v>
+                  <c:v>0.70669999999999999</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-5.8999999999999999E-3</c:v>
+                  <c:v>5.9999999999999995E-4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2006,16 +2279,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>0.9325</c:v>
+                  <c:v>0.2233</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.6946</c:v>
+                  <c:v>0.60909999999999997</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.88180000000000003</c:v>
-                </c:pt>
-                <c:pt idx="3" formatCode="0.00E+00">
-                  <c:v>-5.0000000000000001E-4</c:v>
+                  <c:v>0.95209999999999995</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.5000000000000001E-3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2069,16 +2342,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>0.50629999999999997</c:v>
+                  <c:v>0.2233</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>9.4799999999999995E-2</c:v>
+                  <c:v>0.76670000000000005</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2.3599999999999999E-2</c:v>
+                  <c:v>0.58650000000000002</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2.5999999999999999E-3</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2132,16 +2405,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>0.56210000000000004</c:v>
+                  <c:v>0.72389999999999999</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.63219999999999998</c:v>
+                  <c:v>0.76629999999999998</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.4612</c:v>
+                  <c:v>0.46899999999999997</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.9E-3</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2195,16 +2468,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>5.1400000000000001E-2</c:v>
+                  <c:v>0.65190000000000003</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.78480000000000005</c:v>
+                  <c:v>9.64E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.5585</c:v>
+                  <c:v>0.64659999999999995</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3.0000000000000001E-3</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2483,16 +2756,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>0.21640000000000001</c:v>
+                  <c:v>0.2233</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.36780000000000002</c:v>
+                  <c:v>0.60909999999999997</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.97230000000000005</c:v>
+                  <c:v>0.95209999999999995</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>6.0000000000000001E-3</c:v>
+                  <c:v>2.5000000000000001E-3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2557,13 +2830,13 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.99709999999999999</c:v>
+                  <c:v>0.27239999999999998</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.28939999999999999</c:v>
+                  <c:v>0.66479999999999995</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>8.0000000000000004E-4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2625,16 +2898,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>0.5534</c:v>
+                  <c:v>0.46189999999999998</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.64849999999999997</c:v>
+                  <c:v>0.39489999999999997</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.77110000000000001</c:v>
+                  <c:v>0.40560000000000002</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.5E-3</c:v>
+                  <c:v>7.9000000000000008E-3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2699,13 +2972,13 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.1275</c:v>
+                  <c:v>0.17130000000000001</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>5.4999999999999997E-3</c:v>
+                  <c:v>0.30859999999999999</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>8.0999999999999996E-3</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6680,7 +6953,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A3:F89"/>
+  <dimension ref="A3:W185"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
@@ -6863,89 +7136,88 @@
         <v>-0.78720000000000001</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="40" spans="1:5" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A40" s="7" t="s">
+    <row r="40" spans="1:5" ht="23" x14ac:dyDescent="0.35">
+      <c r="A40" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="B40" s="8" t="s">
+      <c r="B40" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="C40" s="8" t="s">
+      <c r="C40" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="D40" s="8" t="s">
+      <c r="D40" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="E40" s="8" t="s">
+      <c r="E40" s="12" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A41" s="4" t="s">
+    <row r="41" spans="1:5" ht="23" x14ac:dyDescent="0.35">
+      <c r="A41" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="B41" s="5">
-        <v>0.4728</v>
-      </c>
-      <c r="C41" s="5">
-        <v>0.31559999999999999</v>
-      </c>
-      <c r="D41" s="5">
-        <v>0.25230000000000002</v>
-      </c>
-      <c r="E41" s="5">
-        <v>2.5999999999999999E-3</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A42" s="4" t="s">
+      <c r="B41" s="13">
+        <v>0.2233</v>
+      </c>
+      <c r="C41" s="13">
+        <v>0.60909999999999997</v>
+      </c>
+      <c r="D41" s="13">
+        <v>0.95209999999999995</v>
+      </c>
+      <c r="E41" s="13">
+        <v>2.5000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A42" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="B42" s="5">
-        <v>0.19059999999999999</v>
-      </c>
-      <c r="C42" s="5">
-        <v>0.2429</v>
-      </c>
-      <c r="D42" s="5">
-        <v>3.6299999999999999E-2</v>
-      </c>
-      <c r="E42" s="5">
-        <v>9.5999999999999992E-3</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A43" s="4" t="s">
+      <c r="B42" s="13">
+        <v>0.88470000000000004</v>
+      </c>
+      <c r="C42" s="13">
+        <v>0.85009999999999997</v>
+      </c>
+      <c r="D42" s="13">
+        <v>0.76390000000000002</v>
+      </c>
+      <c r="E42" s="13">
+        <v>4.0000000000000002E-4</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A43" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="B43" s="5">
-        <v>9.1700000000000004E-2</v>
-      </c>
-      <c r="C43" s="5">
-        <v>0.76339999999999997</v>
-      </c>
-      <c r="D43" s="5">
-        <v>0.3493</v>
-      </c>
-      <c r="E43" s="5">
-        <v>2.5999999999999999E-3</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A44" s="4" t="s">
+      <c r="B43" s="13">
+        <v>0.70409999999999995</v>
+      </c>
+      <c r="C43" s="13">
+        <v>0.59050000000000002</v>
+      </c>
+      <c r="D43" s="13">
+        <v>0.51070000000000004</v>
+      </c>
+      <c r="E43" s="13">
+        <v>2.5000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" ht="23" x14ac:dyDescent="0.35">
+      <c r="A44" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="B44" s="5">
+      <c r="B44" s="13">
         <v>1</v>
       </c>
-      <c r="C44" s="5">
+      <c r="C44" s="13">
         <v>0</v>
       </c>
-      <c r="D44" s="5">
+      <c r="D44" s="13">
         <v>0</v>
       </c>
-      <c r="E44" s="5">
+      <c r="E44" s="13">
         <v>-0.5</v>
       </c>
     </row>
@@ -6967,72 +7239,72 @@
         <v>8</v>
       </c>
     </row>
-    <row r="53" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A53" s="4">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A53" s="13">
         <v>2</v>
       </c>
-      <c r="B53" s="5">
-        <v>0.50170000000000003</v>
-      </c>
-      <c r="C53" s="5">
+      <c r="B53" s="13">
+        <v>0.69269999999999998</v>
+      </c>
+      <c r="C53" s="13">
         <v>0</v>
       </c>
-      <c r="D53" s="5">
+      <c r="D53" s="13">
         <v>0</v>
       </c>
-      <c r="E53" s="5">
-        <v>4.4299999999999999E-2</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A54" s="4">
+      <c r="E53" s="13">
+        <v>4.6100000000000002E-2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A54" s="13">
         <v>4</v>
       </c>
-      <c r="B54" s="5">
-        <v>0.40229999999999999</v>
-      </c>
-      <c r="C54" s="5">
-        <v>1.0800000000000001E-2</v>
-      </c>
-      <c r="D54" s="5">
-        <v>4.7000000000000002E-3</v>
-      </c>
-      <c r="E54" s="5">
-        <v>-6.1999999999999998E-3</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A55" s="4">
+      <c r="B54" s="13">
+        <v>0.82230000000000003</v>
+      </c>
+      <c r="C54" s="13">
+        <v>6.9999999999999999E-4</v>
+      </c>
+      <c r="D54" s="13">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="E54" s="13" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A55" s="13">
         <v>8</v>
       </c>
-      <c r="B55" s="5">
-        <v>0.75160000000000005</v>
-      </c>
-      <c r="C55" s="5">
-        <v>0.69920000000000004</v>
-      </c>
-      <c r="D55" s="5">
-        <v>0.46899999999999997</v>
-      </c>
-      <c r="E55" s="5">
-        <v>-5.8999999999999999E-3</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A56" s="4">
+      <c r="B55" s="13">
+        <v>0.2233</v>
+      </c>
+      <c r="C55" s="13">
+        <v>0.60909999999999997</v>
+      </c>
+      <c r="D55" s="13">
+        <v>0.95209999999999995</v>
+      </c>
+      <c r="E55" s="13">
+        <v>2.5000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A56" s="13">
         <v>16</v>
       </c>
-      <c r="B56" s="5">
-        <v>0.34970000000000001</v>
-      </c>
-      <c r="C56" s="5">
-        <v>0.96120000000000005</v>
-      </c>
-      <c r="D56" s="5">
-        <v>0.92190000000000005</v>
-      </c>
-      <c r="E56" s="5">
-        <v>1.2999999999999999E-3</v>
+      <c r="B56" s="13">
+        <v>0.48359999999999997</v>
+      </c>
+      <c r="C56" s="13">
+        <v>0.18559999999999999</v>
+      </c>
+      <c r="D56" s="13">
+        <v>5.57E-2</v>
+      </c>
+      <c r="E56" s="13">
+        <v>5.0000000000000001E-3</v>
       </c>
     </row>
     <row r="69" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
@@ -7053,112 +7325,112 @@
         <v>8</v>
       </c>
     </row>
-    <row r="71" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A71" s="4">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A71" s="13">
         <v>1</v>
       </c>
-      <c r="B71" s="5">
-        <v>0.97150000000000003</v>
-      </c>
-      <c r="C71" s="5">
-        <v>0.54900000000000004</v>
-      </c>
-      <c r="D71" s="5">
-        <v>0.2198</v>
-      </c>
-      <c r="E71" s="5">
-        <v>-5.7999999999999996E-3</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A72" s="4">
+      <c r="B71" s="13">
+        <v>0.61929999999999996</v>
+      </c>
+      <c r="C71" s="13">
+        <v>0.76839999999999997</v>
+      </c>
+      <c r="D71" s="13">
+        <v>0.44409999999999999</v>
+      </c>
+      <c r="E71" s="13">
+        <v>6.9999999999999999E-4</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A72" s="13">
         <v>2</v>
       </c>
-      <c r="B72" s="5">
-        <v>0.25800000000000001</v>
-      </c>
-      <c r="C72" s="5">
-        <v>0.63759999999999994</v>
-      </c>
-      <c r="D72" s="5">
-        <v>0.54169999999999996</v>
-      </c>
-      <c r="E72" s="5">
-        <v>-5.8999999999999999E-3</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A73" s="4">
+      <c r="B72" s="13">
+        <v>0.88770000000000004</v>
+      </c>
+      <c r="C72" s="13">
+        <v>0.70789999999999997</v>
+      </c>
+      <c r="D72" s="13">
+        <v>0.70669999999999999</v>
+      </c>
+      <c r="E72" s="13">
+        <v>5.9999999999999995E-4</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A73" s="13">
         <v>3</v>
       </c>
-      <c r="B73" s="5">
-        <v>0.9325</v>
-      </c>
-      <c r="C73" s="5">
-        <v>0.6946</v>
-      </c>
-      <c r="D73" s="5">
-        <v>0.88180000000000003</v>
-      </c>
-      <c r="E73" s="9">
-        <v>-5.0000000000000001E-4</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A74" s="4">
+      <c r="B73" s="13">
+        <v>0.2233</v>
+      </c>
+      <c r="C73" s="13">
+        <v>0.60909999999999997</v>
+      </c>
+      <c r="D73" s="13">
+        <v>0.95209999999999995</v>
+      </c>
+      <c r="E73" s="13">
+        <v>2.5000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A74" s="13">
         <v>4</v>
       </c>
-      <c r="B74" s="5">
-        <v>0.50629999999999997</v>
-      </c>
-      <c r="C74" s="5">
-        <v>9.4799999999999995E-2</v>
-      </c>
-      <c r="D74" s="5">
-        <v>2.3599999999999999E-2</v>
-      </c>
-      <c r="E74" s="5">
-        <v>2.5999999999999999E-3</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A75" s="4">
+      <c r="B74" s="13">
+        <v>0.2233</v>
+      </c>
+      <c r="C74" s="13">
+        <v>0.76670000000000005</v>
+      </c>
+      <c r="D74" s="13">
+        <v>0.58650000000000002</v>
+      </c>
+      <c r="E74" s="13" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A75" s="13">
         <v>5</v>
       </c>
-      <c r="B75" s="5">
-        <v>0.56210000000000004</v>
-      </c>
-      <c r="C75" s="5">
-        <v>0.63219999999999998</v>
-      </c>
-      <c r="D75" s="5">
-        <v>0.4612</v>
-      </c>
-      <c r="E75" s="5">
-        <v>1.9E-3</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A76" s="4">
+      <c r="B75" s="13">
+        <v>0.72389999999999999</v>
+      </c>
+      <c r="C75" s="13">
+        <v>0.76629999999999998</v>
+      </c>
+      <c r="D75" s="13">
+        <v>0.46899999999999997</v>
+      </c>
+      <c r="E75" s="13" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A76" s="13">
         <v>6</v>
       </c>
-      <c r="B76" s="5">
-        <v>5.1400000000000001E-2</v>
-      </c>
-      <c r="C76" s="5">
-        <v>0.78480000000000005</v>
-      </c>
-      <c r="D76" s="5">
-        <v>0.5585</v>
-      </c>
-      <c r="E76" s="5">
-        <v>3.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="85" spans="1:6" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B76" s="13">
+        <v>0.65190000000000003</v>
+      </c>
+      <c r="C76" s="13">
+        <v>9.64E-2</v>
+      </c>
+      <c r="D76" s="13">
+        <v>0.64659999999999995</v>
+      </c>
+      <c r="E76" s="13" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="84" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="85" spans="1:21" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A85" s="7" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B85" s="8" t="s">
         <v>5</v>
@@ -7173,87 +7445,2701 @@
         <v>8</v>
       </c>
       <c r="F85" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="86" spans="1:21" ht="52.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A86" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B86" s="13">
+        <v>0.2233</v>
+      </c>
+      <c r="C86" s="13">
+        <v>0.60909999999999997</v>
+      </c>
+      <c r="D86" s="13">
+        <v>0.95209999999999995</v>
+      </c>
+      <c r="E86" s="13">
+        <v>2.5000000000000001E-3</v>
+      </c>
+      <c r="F86" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="87" spans="1:21" ht="52.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A87" s="4" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="86" spans="1:6" ht="52.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A86" s="4" t="s">
+      <c r="B87" s="15">
+        <v>0</v>
+      </c>
+      <c r="C87" s="13">
+        <v>0.27239999999999998</v>
+      </c>
+      <c r="D87" s="13">
+        <v>0.66479999999999995</v>
+      </c>
+      <c r="E87" s="13">
+        <v>8.0000000000000004E-4</v>
+      </c>
+      <c r="F87" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="88" spans="1:21" ht="39.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A88" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B88" s="13">
+        <v>0.46189999999999998</v>
+      </c>
+      <c r="C88" s="13">
+        <v>0.39489999999999997</v>
+      </c>
+      <c r="D88" s="13">
+        <v>0.40560000000000002</v>
+      </c>
+      <c r="E88" s="13">
+        <v>7.9000000000000008E-3</v>
+      </c>
+      <c r="F88" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="89" spans="1:21" ht="39.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A89" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B89" s="15">
+        <v>0</v>
+      </c>
+      <c r="C89" s="13">
+        <v>0.17130000000000001</v>
+      </c>
+      <c r="D89" s="13">
+        <v>0.30859999999999999</v>
+      </c>
+      <c r="E89" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="F89" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="93" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A93" t="s">
         <v>22</v>
       </c>
-      <c r="B86" s="5">
-        <v>0.21640000000000001</v>
-      </c>
-      <c r="C86" s="5">
-        <v>0.36780000000000002</v>
-      </c>
-      <c r="D86" s="5">
-        <v>0.97230000000000005</v>
-      </c>
-      <c r="E86" s="5">
-        <v>6.0000000000000001E-3</v>
-      </c>
-      <c r="F86" s="5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6" ht="52.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A87" s="4" t="s">
+    </row>
+    <row r="95" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A95" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q95" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="96" spans="1:21" ht="34.5" x14ac:dyDescent="0.35">
+      <c r="A96" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="B96" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="C96" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="D96" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="E96" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F96" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="B87" s="5">
+      <c r="G96" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="H96" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="I96" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="J96" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="K96" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="L96" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="M96" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q96" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="R96" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="S96" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="T96" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="U96" s="12" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="97" spans="1:21" ht="34.5" x14ac:dyDescent="0.35">
+      <c r="A97" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="B97" s="13">
+        <v>0.2233</v>
+      </c>
+      <c r="C97" s="13">
+        <v>0.60909999999999997</v>
+      </c>
+      <c r="D97" s="13">
+        <v>0.95209999999999995</v>
+      </c>
+      <c r="E97" s="13">
+        <v>2.5000000000000001E-3</v>
+      </c>
+      <c r="F97" s="13">
+        <v>1.5849</v>
+      </c>
+      <c r="G97" s="13">
+        <v>4.0000000000000003E-5</v>
+      </c>
+      <c r="H97" s="13">
+        <v>4.0000000000000003E-5</v>
+      </c>
+      <c r="I97" s="13">
+        <v>0.93540000000000001</v>
+      </c>
+      <c r="J97" s="13">
+        <v>0.39290000000000003</v>
+      </c>
+      <c r="K97" s="13">
+        <v>0.82389999999999997</v>
+      </c>
+      <c r="L97" s="13">
+        <v>25001</v>
+      </c>
+      <c r="M97" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q97" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="R97" s="13">
+        <v>0.2233</v>
+      </c>
+      <c r="S97" s="13">
+        <v>0.88470000000000004</v>
+      </c>
+      <c r="T97" s="13">
+        <v>0.70409999999999995</v>
+      </c>
+      <c r="U97" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:21" ht="34.5" x14ac:dyDescent="0.35">
+      <c r="A98" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="B98" s="13">
+        <v>0.88470000000000004</v>
+      </c>
+      <c r="C98" s="13">
+        <v>0.85009999999999997</v>
+      </c>
+      <c r="D98" s="13">
+        <v>0.76390000000000002</v>
+      </c>
+      <c r="E98" s="13">
+        <v>4.0000000000000002E-4</v>
+      </c>
+      <c r="F98" s="13">
+        <v>1.585</v>
+      </c>
+      <c r="G98" s="13">
+        <v>2.0000000000000002E-5</v>
+      </c>
+      <c r="H98" s="13">
+        <v>3.0000000000000001E-5</v>
+      </c>
+      <c r="I98" s="13">
+        <v>0.23780000000000001</v>
+      </c>
+      <c r="J98" s="13">
+        <v>0.98550000000000004</v>
+      </c>
+      <c r="K98" s="13">
+        <v>0.46839999999999998</v>
+      </c>
+      <c r="L98" s="13">
+        <v>25000</v>
+      </c>
+      <c r="M98" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q98" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="R98" s="13">
+        <v>0.60909999999999997</v>
+      </c>
+      <c r="S98" s="13">
+        <v>0.85009999999999997</v>
+      </c>
+      <c r="T98" s="13">
+        <v>0.59050000000000002</v>
+      </c>
+      <c r="U98" s="13">
         <v>0</v>
       </c>
-      <c r="C87" s="5">
-        <v>0.99709999999999999</v>
-      </c>
-      <c r="D87" s="5">
-        <v>0.28939999999999999</v>
-      </c>
-      <c r="E87" s="5">
+    </row>
+    <row r="99" spans="1:21" ht="34.5" x14ac:dyDescent="0.35">
+      <c r="A99" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="B99" s="13">
+        <v>0.70409999999999995</v>
+      </c>
+      <c r="C99" s="13">
+        <v>0.59050000000000002</v>
+      </c>
+      <c r="D99" s="13">
+        <v>0.51070000000000004</v>
+      </c>
+      <c r="E99" s="13">
+        <v>2.5000000000000001E-3</v>
+      </c>
+      <c r="F99" s="13">
+        <v>1.585</v>
+      </c>
+      <c r="G99" s="13">
+        <v>4.0000000000000003E-5</v>
+      </c>
+      <c r="H99" s="13">
+        <v>6.0000000000000002E-5</v>
+      </c>
+      <c r="I99" s="13">
+        <v>0.60160000000000002</v>
+      </c>
+      <c r="J99" s="13">
+        <v>0.19800000000000001</v>
+      </c>
+      <c r="K99" s="13">
+        <v>0.58879999999999999</v>
+      </c>
+      <c r="L99" s="13">
+        <v>25000</v>
+      </c>
+      <c r="M99" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q99" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="R99" s="13">
+        <v>0.95209999999999995</v>
+      </c>
+      <c r="S99" s="13">
+        <v>0.76390000000000002</v>
+      </c>
+      <c r="T99" s="13">
+        <v>0.51070000000000004</v>
+      </c>
+      <c r="U99" s="13">
         <v>0</v>
       </c>
-      <c r="F87" s="5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6" ht="39.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A88" s="4" t="s">
+    </row>
+    <row r="100" spans="1:21" ht="69" x14ac:dyDescent="0.35">
+      <c r="A100" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="B100" s="13">
+        <v>1</v>
+      </c>
+      <c r="C100" s="13">
+        <v>0</v>
+      </c>
+      <c r="D100" s="13">
+        <v>0</v>
+      </c>
+      <c r="E100" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="F100" s="13">
+        <v>1.585</v>
+      </c>
+      <c r="G100" s="13">
+        <v>1.5849599999999999</v>
+      </c>
+      <c r="H100" s="13">
+        <v>1.5849599999999999</v>
+      </c>
+      <c r="I100" s="13">
+        <v>0</v>
+      </c>
+      <c r="J100" s="13">
+        <v>0</v>
+      </c>
+      <c r="K100" s="13">
+        <v>0</v>
+      </c>
+      <c r="L100" s="13">
+        <v>2</v>
+      </c>
+      <c r="M100" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q100" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="R100" s="13">
+        <v>2.5000000000000001E-3</v>
+      </c>
+      <c r="S100" s="13">
+        <v>4.0000000000000002E-4</v>
+      </c>
+      <c r="T100" s="13">
+        <v>2.5000000000000001E-3</v>
+      </c>
+      <c r="U100" s="13" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="101" spans="1:21" ht="23" x14ac:dyDescent="0.35">
+      <c r="Q101" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="R101" s="13">
+        <v>1.5849</v>
+      </c>
+      <c r="S101" s="13">
+        <v>1.585</v>
+      </c>
+      <c r="T101" s="13">
+        <v>1.585</v>
+      </c>
+      <c r="U101" s="13">
+        <v>1.585</v>
+      </c>
+    </row>
+    <row r="102" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A102" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q102" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="B88" s="5">
-        <v>0.5534</v>
-      </c>
-      <c r="C88" s="5">
-        <v>0.64849999999999997</v>
-      </c>
-      <c r="D88" s="5">
-        <v>0.77110000000000001</v>
-      </c>
-      <c r="E88" s="5">
-        <v>1.5E-3</v>
-      </c>
-      <c r="F88" s="5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6" ht="39.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A89" s="4" t="s">
+      <c r="R102" s="13">
+        <v>4.0000000000000003E-5</v>
+      </c>
+      <c r="S102" s="13">
+        <v>2.0000000000000002E-5</v>
+      </c>
+      <c r="T102" s="13">
+        <v>4.0000000000000003E-5</v>
+      </c>
+      <c r="U102" s="13">
+        <v>1.5849599999999999</v>
+      </c>
+    </row>
+    <row r="103" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="Q103" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="B89" s="5">
+      <c r="R103" s="13">
+        <v>4.0000000000000003E-5</v>
+      </c>
+      <c r="S103" s="13">
+        <v>3.0000000000000001E-5</v>
+      </c>
+      <c r="T103" s="13">
+        <v>6.0000000000000002E-5</v>
+      </c>
+      <c r="U103" s="13">
+        <v>1.5849599999999999</v>
+      </c>
+    </row>
+    <row r="104" spans="1:21" ht="34.5" x14ac:dyDescent="0.35">
+      <c r="A104" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="B104" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="C104" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="D104" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="E104" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F104" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="G104" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="H104" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="I104" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="J104" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="K104" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="L104" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="M104" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q104" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="R104" s="13">
+        <v>0.93540000000000001</v>
+      </c>
+      <c r="S104" s="13">
+        <v>0.23780000000000001</v>
+      </c>
+      <c r="T104" s="13">
+        <v>0.60160000000000002</v>
+      </c>
+      <c r="U104" s="13">
         <v>0</v>
       </c>
-      <c r="C89" s="5">
-        <v>0.1275</v>
-      </c>
-      <c r="D89" s="5">
-        <v>5.4999999999999997E-3</v>
-      </c>
-      <c r="E89" s="5">
-        <v>8.0999999999999996E-3</v>
-      </c>
-      <c r="F89" s="5" t="s">
-        <v>21</v>
+    </row>
+    <row r="105" spans="1:21" ht="57.5" x14ac:dyDescent="0.35">
+      <c r="A105" s="13">
+        <v>2</v>
+      </c>
+      <c r="B105" s="13">
+        <v>0.69269999999999998</v>
+      </c>
+      <c r="C105" s="13">
+        <v>0</v>
+      </c>
+      <c r="D105" s="13">
+        <v>0</v>
+      </c>
+      <c r="E105" s="13">
+        <v>4.6100000000000002E-2</v>
+      </c>
+      <c r="F105" s="13">
+        <v>1.585</v>
+      </c>
+      <c r="G105" s="13">
+        <v>9.4699999999999993E-3</v>
+      </c>
+      <c r="H105" s="13">
+        <v>3.6999999999999999E-4</v>
+      </c>
+      <c r="I105" s="13">
+        <v>0</v>
+      </c>
+      <c r="J105" s="13">
+        <v>0</v>
+      </c>
+      <c r="K105" s="13">
+        <v>0</v>
+      </c>
+      <c r="L105" s="13">
+        <v>25000</v>
+      </c>
+      <c r="M105" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q105" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="R105" s="13">
+        <v>0.39290000000000003</v>
+      </c>
+      <c r="S105" s="13">
+        <v>0.98550000000000004</v>
+      </c>
+      <c r="T105" s="13">
+        <v>0.19800000000000001</v>
+      </c>
+      <c r="U105" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:21" ht="80.5" x14ac:dyDescent="0.35">
+      <c r="A106" s="13">
+        <v>4</v>
+      </c>
+      <c r="B106" s="13">
+        <v>0.82230000000000003</v>
+      </c>
+      <c r="C106" s="13">
+        <v>6.9999999999999999E-4</v>
+      </c>
+      <c r="D106" s="13">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="E106" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="F106" s="13">
+        <v>1.585</v>
+      </c>
+      <c r="G106" s="13">
+        <v>2.7999999999999998E-4</v>
+      </c>
+      <c r="H106" s="13">
+        <v>2.0000000000000002E-5</v>
+      </c>
+      <c r="I106" s="13">
+        <v>1.4500000000000001E-2</v>
+      </c>
+      <c r="J106" s="13">
+        <v>5.67E-2</v>
+      </c>
+      <c r="K106" s="13">
+        <v>0.73750000000000004</v>
+      </c>
+      <c r="L106" s="13">
+        <v>25000</v>
+      </c>
+      <c r="M106" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q106" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="R106" s="13">
+        <v>0.82389999999999997</v>
+      </c>
+      <c r="S106" s="13">
+        <v>0.46839999999999998</v>
+      </c>
+      <c r="T106" s="13">
+        <v>0.58879999999999999</v>
+      </c>
+      <c r="U106" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:21" ht="46" x14ac:dyDescent="0.35">
+      <c r="A107" s="13">
+        <v>8</v>
+      </c>
+      <c r="B107" s="13">
+        <v>0.2233</v>
+      </c>
+      <c r="C107" s="13">
+        <v>0.60909999999999997</v>
+      </c>
+      <c r="D107" s="13">
+        <v>0.95209999999999995</v>
+      </c>
+      <c r="E107" s="13">
+        <v>2.5000000000000001E-3</v>
+      </c>
+      <c r="F107" s="13">
+        <v>1.5849</v>
+      </c>
+      <c r="G107" s="13">
+        <v>4.0000000000000003E-5</v>
+      </c>
+      <c r="H107" s="13">
+        <v>4.0000000000000003E-5</v>
+      </c>
+      <c r="I107" s="13">
+        <v>0.93540000000000001</v>
+      </c>
+      <c r="J107" s="13">
+        <v>0.39290000000000003</v>
+      </c>
+      <c r="K107" s="13">
+        <v>0.82389999999999997</v>
+      </c>
+      <c r="L107" s="13">
+        <v>25001</v>
+      </c>
+      <c r="M107" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q107" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="R107" s="13">
+        <v>25001</v>
+      </c>
+      <c r="S107" s="13">
+        <v>25000</v>
+      </c>
+      <c r="T107" s="13">
+        <v>25000</v>
+      </c>
+      <c r="U107" s="13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="108" spans="1:21" ht="92" x14ac:dyDescent="0.35">
+      <c r="A108" s="13">
+        <v>16</v>
+      </c>
+      <c r="B108" s="13">
+        <v>0.48359999999999997</v>
+      </c>
+      <c r="C108" s="13">
+        <v>0.18559999999999999</v>
+      </c>
+      <c r="D108" s="13">
+        <v>5.57E-2</v>
+      </c>
+      <c r="E108" s="13">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="F108" s="13">
+        <v>1.5849</v>
+      </c>
+      <c r="G108" s="13">
+        <v>9.0000000000000006E-5</v>
+      </c>
+      <c r="H108" s="13">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="I108" s="13">
+        <v>1.3599999999999999E-2</v>
+      </c>
+      <c r="J108" s="13">
+        <v>0.33510000000000001</v>
+      </c>
+      <c r="K108" s="13">
+        <v>0.53120000000000001</v>
+      </c>
+      <c r="L108" s="13">
+        <v>25000</v>
+      </c>
+      <c r="M108" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q108" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="R108" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="S108" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="T108" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="U108" s="13" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="110" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A110" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q110" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="111" spans="1:21" ht="34.5" x14ac:dyDescent="0.35">
+      <c r="A111" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="B111" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="C111" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="D111" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="E111" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F111" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="G111" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="H111" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="I111" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="J111" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="K111" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="L111" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="M111" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q111" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="R111" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="S111" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="T111" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="U111" s="12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="112" spans="1:21" ht="34.5" x14ac:dyDescent="0.35">
+      <c r="A112" s="13">
+        <v>1</v>
+      </c>
+      <c r="B112" s="13">
+        <v>0.61929999999999996</v>
+      </c>
+      <c r="C112" s="13">
+        <v>0.76839999999999997</v>
+      </c>
+      <c r="D112" s="13">
+        <v>0.44409999999999999</v>
+      </c>
+      <c r="E112" s="13">
+        <v>6.9999999999999999E-4</v>
+      </c>
+      <c r="F112" s="13">
+        <v>1.5849</v>
+      </c>
+      <c r="G112" s="13">
+        <v>3.0000000000000001E-5</v>
+      </c>
+      <c r="H112" s="13">
+        <v>6.0000000000000002E-5</v>
+      </c>
+      <c r="I112" s="13">
+        <v>0.14360000000000001</v>
+      </c>
+      <c r="J112" s="13">
+        <v>0.57620000000000005</v>
+      </c>
+      <c r="K112" s="13">
+        <v>0.74370000000000003</v>
+      </c>
+      <c r="L112" s="13">
+        <v>25000</v>
+      </c>
+      <c r="M112" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q112" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="R112" s="13">
+        <v>0.69269999999999998</v>
+      </c>
+      <c r="S112" s="13">
+        <v>0.82230000000000003</v>
+      </c>
+      <c r="T112" s="13">
+        <v>0.2233</v>
+      </c>
+      <c r="U112" s="13">
+        <v>0.48359999999999997</v>
+      </c>
+    </row>
+    <row r="113" spans="1:23" ht="34.5" x14ac:dyDescent="0.35">
+      <c r="A113" s="13">
+        <v>2</v>
+      </c>
+      <c r="B113" s="13">
+        <v>0.88770000000000004</v>
+      </c>
+      <c r="C113" s="13">
+        <v>0.70789999999999997</v>
+      </c>
+      <c r="D113" s="13">
+        <v>0.70669999999999999</v>
+      </c>
+      <c r="E113" s="13">
+        <v>5.9999999999999995E-4</v>
+      </c>
+      <c r="F113" s="13">
+        <v>1.585</v>
+      </c>
+      <c r="G113" s="13">
+        <v>3.0000000000000001E-5</v>
+      </c>
+      <c r="H113" s="13">
+        <v>3.0000000000000001E-5</v>
+      </c>
+      <c r="I113" s="13">
+        <v>0.77959999999999996</v>
+      </c>
+      <c r="J113" s="13">
+        <v>0.63460000000000005</v>
+      </c>
+      <c r="K113" s="13">
+        <v>0.32940000000000003</v>
+      </c>
+      <c r="L113" s="13">
+        <v>25000</v>
+      </c>
+      <c r="M113" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q113" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="R113" s="13">
+        <v>0</v>
+      </c>
+      <c r="S113" s="13">
+        <v>6.9999999999999999E-4</v>
+      </c>
+      <c r="T113" s="13">
+        <v>0.60909999999999997</v>
+      </c>
+      <c r="U113" s="13">
+        <v>0.18559999999999999</v>
+      </c>
+    </row>
+    <row r="114" spans="1:23" ht="34.5" x14ac:dyDescent="0.35">
+      <c r="A114" s="13">
+        <v>3</v>
+      </c>
+      <c r="B114" s="13">
+        <v>0.2233</v>
+      </c>
+      <c r="C114" s="13">
+        <v>0.60909999999999997</v>
+      </c>
+      <c r="D114" s="13">
+        <v>0.95209999999999995</v>
+      </c>
+      <c r="E114" s="13">
+        <v>2.5000000000000001E-3</v>
+      </c>
+      <c r="F114" s="13">
+        <v>1.5849</v>
+      </c>
+      <c r="G114" s="13">
+        <v>4.0000000000000003E-5</v>
+      </c>
+      <c r="H114" s="13">
+        <v>4.0000000000000003E-5</v>
+      </c>
+      <c r="I114" s="13">
+        <v>0.93540000000000001</v>
+      </c>
+      <c r="J114" s="13">
+        <v>0.39290000000000003</v>
+      </c>
+      <c r="K114" s="13">
+        <v>0.82389999999999997</v>
+      </c>
+      <c r="L114" s="13">
+        <v>25001</v>
+      </c>
+      <c r="M114" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q114" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="R114" s="13">
+        <v>0</v>
+      </c>
+      <c r="S114" s="13">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="T114" s="13">
+        <v>0.95209999999999995</v>
+      </c>
+      <c r="U114" s="13">
+        <v>5.57E-2</v>
+      </c>
+    </row>
+    <row r="115" spans="1:23" ht="34.5" x14ac:dyDescent="0.35">
+      <c r="A115" s="13">
+        <v>4</v>
+      </c>
+      <c r="B115" s="13">
+        <v>0.2233</v>
+      </c>
+      <c r="C115" s="13">
+        <v>0.76670000000000005</v>
+      </c>
+      <c r="D115" s="13">
+        <v>0.58650000000000002</v>
+      </c>
+      <c r="E115" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="F115" s="13">
+        <v>1.5849</v>
+      </c>
+      <c r="G115" s="13">
+        <v>3.0000000000000001E-5</v>
+      </c>
+      <c r="H115" s="13">
+        <v>5.0000000000000002E-5</v>
+      </c>
+      <c r="I115" s="13">
+        <v>0.55630000000000002</v>
+      </c>
+      <c r="J115" s="13">
+        <v>0.62319999999999998</v>
+      </c>
+      <c r="K115" s="13">
+        <v>0.59199999999999997</v>
+      </c>
+      <c r="L115" s="13">
+        <v>25000</v>
+      </c>
+      <c r="M115" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q115" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="R115" s="13">
+        <v>4.6100000000000002E-2</v>
+      </c>
+      <c r="S115" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="T115" s="13">
+        <v>2.5000000000000001E-3</v>
+      </c>
+      <c r="U115" s="13">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="116" spans="1:23" ht="34.5" x14ac:dyDescent="0.35">
+      <c r="A116" s="13">
+        <v>5</v>
+      </c>
+      <c r="B116" s="13">
+        <v>0.72389999999999999</v>
+      </c>
+      <c r="C116" s="13">
+        <v>0.76629999999999998</v>
+      </c>
+      <c r="D116" s="13">
+        <v>0.46899999999999997</v>
+      </c>
+      <c r="E116" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="F116" s="13">
+        <v>1.585</v>
+      </c>
+      <c r="G116" s="13">
+        <v>3.0000000000000001E-5</v>
+      </c>
+      <c r="H116" s="13">
+        <v>5.0000000000000002E-5</v>
+      </c>
+      <c r="I116" s="13">
+        <v>0.93489999999999995</v>
+      </c>
+      <c r="J116" s="13">
+        <v>0.7883</v>
+      </c>
+      <c r="K116" s="13">
+        <v>0.3009</v>
+      </c>
+      <c r="L116" s="13">
+        <v>25000</v>
+      </c>
+      <c r="M116" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q116" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="R116" s="13">
+        <v>1.585</v>
+      </c>
+      <c r="S116" s="13">
+        <v>1.585</v>
+      </c>
+      <c r="T116" s="13">
+        <v>1.5849</v>
+      </c>
+      <c r="U116" s="13">
+        <v>1.5849</v>
+      </c>
+    </row>
+    <row r="117" spans="1:23" ht="80.5" x14ac:dyDescent="0.35">
+      <c r="A117" s="13">
+        <v>6</v>
+      </c>
+      <c r="B117" s="13">
+        <v>0.65190000000000003</v>
+      </c>
+      <c r="C117" s="13">
+        <v>9.64E-2</v>
+      </c>
+      <c r="D117" s="13">
+        <v>0.64659999999999995</v>
+      </c>
+      <c r="E117" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="F117" s="13">
+        <v>1.585</v>
+      </c>
+      <c r="G117" s="13">
+        <v>1.1E-4</v>
+      </c>
+      <c r="H117" s="13">
+        <v>3.0000000000000001E-5</v>
+      </c>
+      <c r="I117" s="13">
+        <v>0.50049999999999994</v>
+      </c>
+      <c r="J117" s="13">
+        <v>0.14449999999999999</v>
+      </c>
+      <c r="K117" s="13">
+        <v>0.10589999999999999</v>
+      </c>
+      <c r="L117" s="13">
+        <v>25000</v>
+      </c>
+      <c r="M117" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q117" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="R117" s="13">
+        <v>9.4699999999999993E-3</v>
+      </c>
+      <c r="S117" s="13">
+        <v>2.7999999999999998E-4</v>
+      </c>
+      <c r="T117" s="13">
+        <v>4.0000000000000003E-5</v>
+      </c>
+      <c r="U117" s="13">
+        <v>9.0000000000000006E-5</v>
+      </c>
+    </row>
+    <row r="118" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="Q118" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="R118" s="13">
+        <v>3.6999999999999999E-4</v>
+      </c>
+      <c r="S118" s="13">
+        <v>2.0000000000000002E-5</v>
+      </c>
+      <c r="T118" s="13">
+        <v>4.0000000000000003E-5</v>
+      </c>
+      <c r="U118" s="13">
+        <v>1.0000000000000001E-5</v>
+      </c>
+    </row>
+    <row r="119" spans="1:23" ht="23" x14ac:dyDescent="0.35">
+      <c r="Q119" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="R119" s="13">
+        <v>0</v>
+      </c>
+      <c r="S119" s="13">
+        <v>1.4500000000000001E-2</v>
+      </c>
+      <c r="T119" s="13">
+        <v>0.93540000000000001</v>
+      </c>
+      <c r="U119" s="13">
+        <v>1.3599999999999999E-2</v>
+      </c>
+    </row>
+    <row r="120" spans="1:23" ht="23" x14ac:dyDescent="0.35">
+      <c r="A120" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q120" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="R120" s="13">
+        <v>0</v>
+      </c>
+      <c r="S120" s="13">
+        <v>5.67E-2</v>
+      </c>
+      <c r="T120" s="13">
+        <v>0.39290000000000003</v>
+      </c>
+      <c r="U120" s="13">
+        <v>0.33510000000000001</v>
+      </c>
+    </row>
+    <row r="121" spans="1:23" ht="34.5" x14ac:dyDescent="0.35">
+      <c r="A121" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B121" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C121" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="D121" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="E121" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="F121" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="G121" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H121" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="I121" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="J121" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="K121" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="L121" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="M121" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="N121" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q121" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="R121" s="13">
+        <v>0</v>
+      </c>
+      <c r="S121" s="13">
+        <v>0.73750000000000004</v>
+      </c>
+      <c r="T121" s="13">
+        <v>0.82389999999999997</v>
+      </c>
+      <c r="U121" s="13">
+        <v>0.53120000000000001</v>
+      </c>
+    </row>
+    <row r="122" spans="1:23" ht="34.5" x14ac:dyDescent="0.35">
+      <c r="A122" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="B122" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C122" s="13">
+        <v>0.2233</v>
+      </c>
+      <c r="D122" s="13">
+        <v>0.60909999999999997</v>
+      </c>
+      <c r="E122" s="13">
+        <v>0.95209999999999995</v>
+      </c>
+      <c r="F122" s="13">
+        <v>2.5000000000000001E-3</v>
+      </c>
+      <c r="G122" s="13">
+        <v>1.5849</v>
+      </c>
+      <c r="H122" s="13">
+        <v>4.0000000000000003E-5</v>
+      </c>
+      <c r="I122" s="13">
+        <v>4.0000000000000003E-5</v>
+      </c>
+      <c r="J122" s="13">
+        <v>0.93540000000000001</v>
+      </c>
+      <c r="K122" s="13">
+        <v>0.39290000000000003</v>
+      </c>
+      <c r="L122" s="13">
+        <v>0.82389999999999997</v>
+      </c>
+      <c r="M122" s="13">
+        <v>25001</v>
+      </c>
+      <c r="N122" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q122" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="R122" s="13">
+        <v>25000</v>
+      </c>
+      <c r="S122" s="13">
+        <v>25000</v>
+      </c>
+      <c r="T122" s="13">
+        <v>25001</v>
+      </c>
+      <c r="U122" s="13">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="123" spans="1:23" ht="57.5" x14ac:dyDescent="0.35">
+      <c r="A123" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="B123" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="C123" s="15">
+        <v>0</v>
+      </c>
+      <c r="D123" s="13">
+        <v>0.27239999999999998</v>
+      </c>
+      <c r="E123" s="13">
+        <v>0.66479999999999995</v>
+      </c>
+      <c r="F123" s="13">
+        <v>8.0000000000000004E-4</v>
+      </c>
+      <c r="G123" s="13">
+        <v>1.5798000000000001</v>
+      </c>
+      <c r="H123" s="13">
+        <v>6.9999999999999994E-5</v>
+      </c>
+      <c r="I123" s="13">
+        <v>3.0000000000000001E-5</v>
+      </c>
+      <c r="J123" s="13">
+        <v>0.7036</v>
+      </c>
+      <c r="K123" s="15">
+        <v>0</v>
+      </c>
+      <c r="L123" s="15">
+        <v>0</v>
+      </c>
+      <c r="M123" s="13">
+        <v>25002</v>
+      </c>
+      <c r="N123" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q123" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="R123" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="S123" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="T123" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="U123" s="13" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="124" spans="1:23" ht="34.5" x14ac:dyDescent="0.35">
+      <c r="A124" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="B124" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C124" s="13">
+        <v>0.46189999999999998</v>
+      </c>
+      <c r="D124" s="13">
+        <v>0.39489999999999997</v>
+      </c>
+      <c r="E124" s="13">
+        <v>0.40560000000000002</v>
+      </c>
+      <c r="F124" s="13">
+        <v>7.9000000000000008E-3</v>
+      </c>
+      <c r="G124" s="13">
+        <v>1.5849</v>
+      </c>
+      <c r="H124" s="13">
+        <v>6.0000000000000002E-5</v>
+      </c>
+      <c r="I124" s="13">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="J124" s="13">
+        <v>0.52</v>
+      </c>
+      <c r="K124" s="13">
+        <v>0.89610000000000001</v>
+      </c>
+      <c r="L124" s="13">
+        <v>0.39450000000000002</v>
+      </c>
+      <c r="M124" s="13">
+        <v>25000</v>
+      </c>
+      <c r="N124" s="13" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="125" spans="1:23" ht="57.5" x14ac:dyDescent="0.35">
+      <c r="A125" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="B125" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="C125" s="15">
+        <v>0</v>
+      </c>
+      <c r="D125" s="13">
+        <v>0.17130000000000001</v>
+      </c>
+      <c r="E125" s="13">
+        <v>0.30859999999999999</v>
+      </c>
+      <c r="F125" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="G125" s="13">
+        <v>1.5789</v>
+      </c>
+      <c r="H125" s="13">
+        <v>9.0000000000000006E-5</v>
+      </c>
+      <c r="I125" s="13">
+        <v>6.9999999999999994E-5</v>
+      </c>
+      <c r="J125" s="13">
+        <v>0.2238</v>
+      </c>
+      <c r="K125" s="15">
+        <v>0</v>
+      </c>
+      <c r="L125" s="15">
+        <v>0</v>
+      </c>
+      <c r="M125" s="13">
+        <v>25000</v>
+      </c>
+      <c r="N125" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q125" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="126" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="Q126" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="R126" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="S126" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="T126" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="U126" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="V126" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="W126" s="12" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="127" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="Q127" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="R127" s="13">
+        <v>0.61929999999999996</v>
+      </c>
+      <c r="S127" s="13">
+        <v>0.88770000000000004</v>
+      </c>
+      <c r="T127" s="13">
+        <v>0.2233</v>
+      </c>
+      <c r="U127" s="13">
+        <v>0.2233</v>
+      </c>
+      <c r="V127" s="13">
+        <v>0.72389999999999999</v>
+      </c>
+      <c r="W127" s="13">
+        <v>0.65190000000000003</v>
+      </c>
+    </row>
+    <row r="128" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A128" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q128" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="R128" s="13">
+        <v>0.76839999999999997</v>
+      </c>
+      <c r="S128" s="13">
+        <v>0.70789999999999997</v>
+      </c>
+      <c r="T128" s="13">
+        <v>0.60909999999999997</v>
+      </c>
+      <c r="U128" s="13">
+        <v>0.76670000000000005</v>
+      </c>
+      <c r="V128" s="13">
+        <v>0.76629999999999998</v>
+      </c>
+      <c r="W128" s="13">
+        <v>9.64E-2</v>
+      </c>
+    </row>
+    <row r="129" spans="1:23" ht="34.5" x14ac:dyDescent="0.35">
+      <c r="A129" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="B129" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="C129" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="D129" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="E129" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F129" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="G129" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="H129" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="I129" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="J129" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="K129" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="L129" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="M129" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q129" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="R129" s="13">
+        <v>0.44409999999999999</v>
+      </c>
+      <c r="S129" s="13">
+        <v>0.70669999999999999</v>
+      </c>
+      <c r="T129" s="13">
+        <v>0.95209999999999995</v>
+      </c>
+      <c r="U129" s="13">
+        <v>0.58650000000000002</v>
+      </c>
+      <c r="V129" s="13">
+        <v>0.46899999999999997</v>
+      </c>
+      <c r="W129" s="13">
+        <v>0.64659999999999995</v>
+      </c>
+    </row>
+    <row r="130" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A130" s="13">
+        <v>0</v>
+      </c>
+      <c r="B130" s="13">
+        <v>0.2233</v>
+      </c>
+      <c r="C130" s="13">
+        <v>0.60909999999999997</v>
+      </c>
+      <c r="D130" s="13">
+        <v>0.95209999999999995</v>
+      </c>
+      <c r="E130" s="13">
+        <v>2.5000000000000001E-3</v>
+      </c>
+      <c r="F130" s="13">
+        <v>1.5849</v>
+      </c>
+      <c r="G130" s="13">
+        <v>4.0000000000000003E-5</v>
+      </c>
+      <c r="H130" s="13">
+        <v>4.0000000000000003E-5</v>
+      </c>
+      <c r="I130" s="13">
+        <v>0.93540000000000001</v>
+      </c>
+      <c r="J130" s="13">
+        <v>0.39290000000000003</v>
+      </c>
+      <c r="K130" s="13">
+        <v>0.82389999999999997</v>
+      </c>
+      <c r="L130" s="13">
+        <v>25001</v>
+      </c>
+      <c r="M130" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q130" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="R130" s="13">
+        <v>6.9999999999999999E-4</v>
+      </c>
+      <c r="S130" s="13">
+        <v>5.9999999999999995E-4</v>
+      </c>
+      <c r="T130" s="13">
+        <v>2.5000000000000001E-3</v>
+      </c>
+      <c r="U130" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="V130" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="W130" s="13" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="131" spans="1:23" ht="23" x14ac:dyDescent="0.35">
+      <c r="A131" s="13">
+        <v>1</v>
+      </c>
+      <c r="B131" s="13">
+        <v>7.4399999999999994E-2</v>
+      </c>
+      <c r="C131" s="13">
+        <v>0.42259999999999998</v>
+      </c>
+      <c r="D131" s="13">
+        <v>0.95209999999999995</v>
+      </c>
+      <c r="E131" s="13">
+        <v>4.7999999999999996E-3</v>
+      </c>
+      <c r="F131" s="13">
+        <v>1.5849</v>
+      </c>
+      <c r="G131" s="13">
+        <v>6.0000000000000002E-5</v>
+      </c>
+      <c r="H131" s="13">
+        <v>2.0000000000000002E-5</v>
+      </c>
+      <c r="I131" s="13">
+        <v>0.44379999999999997</v>
+      </c>
+      <c r="J131" s="13">
+        <v>0.17169999999999999</v>
+      </c>
+      <c r="K131" s="13">
+        <v>0.62829999999999997</v>
+      </c>
+      <c r="L131" s="13">
+        <v>25000</v>
+      </c>
+      <c r="M131" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q131" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="R131" s="13">
+        <v>1.5849</v>
+      </c>
+      <c r="S131" s="13">
+        <v>1.585</v>
+      </c>
+      <c r="T131" s="13">
+        <v>1.5849</v>
+      </c>
+      <c r="U131" s="13">
+        <v>1.5849</v>
+      </c>
+      <c r="V131" s="13">
+        <v>1.585</v>
+      </c>
+      <c r="W131" s="13">
+        <v>1.585</v>
+      </c>
+    </row>
+    <row r="132" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A132" s="13">
+        <v>2</v>
+      </c>
+      <c r="B132" s="13">
+        <v>0.90180000000000005</v>
+      </c>
+      <c r="C132" s="13">
+        <v>0.26860000000000001</v>
+      </c>
+      <c r="D132" s="13">
+        <v>0.27810000000000001</v>
+      </c>
+      <c r="E132" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="F132" s="13">
+        <v>1.585</v>
+      </c>
+      <c r="G132" s="13">
+        <v>6.9999999999999994E-5</v>
+      </c>
+      <c r="H132" s="13">
+        <v>4.0000000000000003E-5</v>
+      </c>
+      <c r="I132" s="13">
+        <v>0.16539999999999999</v>
+      </c>
+      <c r="J132" s="13">
+        <v>0.33639999999999998</v>
+      </c>
+      <c r="K132" s="13">
+        <v>0.97340000000000004</v>
+      </c>
+      <c r="L132" s="13">
+        <v>25000</v>
+      </c>
+      <c r="M132" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q132" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="R132" s="13">
+        <v>3.0000000000000001E-5</v>
+      </c>
+      <c r="S132" s="13">
+        <v>3.0000000000000001E-5</v>
+      </c>
+      <c r="T132" s="13">
+        <v>4.0000000000000003E-5</v>
+      </c>
+      <c r="U132" s="13">
+        <v>3.0000000000000001E-5</v>
+      </c>
+      <c r="V132" s="13">
+        <v>3.0000000000000001E-5</v>
+      </c>
+      <c r="W132" s="13">
+        <v>1.1E-4</v>
+      </c>
+    </row>
+    <row r="133" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A133" s="10"/>
+      <c r="B133" s="10"/>
+      <c r="C133" s="14"/>
+      <c r="D133" s="10"/>
+      <c r="E133" s="10"/>
+      <c r="F133" s="10"/>
+      <c r="G133" s="11"/>
+      <c r="H133" s="14"/>
+      <c r="I133" s="10"/>
+      <c r="J133" s="10"/>
+      <c r="Q133" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="R133" s="13">
+        <v>6.0000000000000002E-5</v>
+      </c>
+      <c r="S133" s="13">
+        <v>3.0000000000000001E-5</v>
+      </c>
+      <c r="T133" s="13">
+        <v>4.0000000000000003E-5</v>
+      </c>
+      <c r="U133" s="13">
+        <v>5.0000000000000002E-5</v>
+      </c>
+      <c r="V133" s="13">
+        <v>5.0000000000000002E-5</v>
+      </c>
+      <c r="W133" s="13">
+        <v>3.0000000000000001E-5</v>
+      </c>
+    </row>
+    <row r="134" spans="1:23" ht="23" x14ac:dyDescent="0.35">
+      <c r="Q134" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="R134" s="13">
+        <v>0.14360000000000001</v>
+      </c>
+      <c r="S134" s="13">
+        <v>0.77959999999999996</v>
+      </c>
+      <c r="T134" s="13">
+        <v>0.93540000000000001</v>
+      </c>
+      <c r="U134" s="13">
+        <v>0.55630000000000002</v>
+      </c>
+      <c r="V134" s="13">
+        <v>0.93489999999999995</v>
+      </c>
+      <c r="W134" s="13">
+        <v>0.50049999999999994</v>
+      </c>
+    </row>
+    <row r="135" spans="1:23" ht="23" x14ac:dyDescent="0.35">
+      <c r="A135" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q135" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="R135" s="13">
+        <v>0.57620000000000005</v>
+      </c>
+      <c r="S135" s="13">
+        <v>0.63460000000000005</v>
+      </c>
+      <c r="T135" s="13">
+        <v>0.39290000000000003</v>
+      </c>
+      <c r="U135" s="13">
+        <v>0.62319999999999998</v>
+      </c>
+      <c r="V135" s="13">
+        <v>0.7883</v>
+      </c>
+      <c r="W135" s="13">
+        <v>0.14449999999999999</v>
+      </c>
+    </row>
+    <row r="136" spans="1:23" ht="34.5" x14ac:dyDescent="0.35">
+      <c r="A136" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="B136" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="C136" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="D136" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="E136" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F136" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="G136" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="H136" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="I136" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="J136" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="K136" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="L136" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="M136" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q136" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="R136" s="13">
+        <v>0.74370000000000003</v>
+      </c>
+      <c r="S136" s="13">
+        <v>0.32940000000000003</v>
+      </c>
+      <c r="T136" s="13">
+        <v>0.82389999999999997</v>
+      </c>
+      <c r="U136" s="13">
+        <v>0.59199999999999997</v>
+      </c>
+      <c r="V136" s="13">
+        <v>0.3009</v>
+      </c>
+      <c r="W136" s="13">
+        <v>0.10589999999999999</v>
+      </c>
+    </row>
+    <row r="137" spans="1:23" ht="46" x14ac:dyDescent="0.35">
+      <c r="A137" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="B137" s="13">
+        <v>0.2233</v>
+      </c>
+      <c r="C137" s="13">
+        <v>0.60909999999999997</v>
+      </c>
+      <c r="D137" s="13">
+        <v>0.95209999999999995</v>
+      </c>
+      <c r="E137" s="13">
+        <v>2.5000000000000001E-3</v>
+      </c>
+      <c r="F137" s="13">
+        <v>1.5849</v>
+      </c>
+      <c r="G137" s="13">
+        <v>4.0000000000000003E-5</v>
+      </c>
+      <c r="H137" s="13">
+        <v>4.0000000000000003E-5</v>
+      </c>
+      <c r="I137" s="13">
+        <v>0.93540000000000001</v>
+      </c>
+      <c r="J137" s="13">
+        <v>0.39290000000000003</v>
+      </c>
+      <c r="K137" s="13">
+        <v>0.82389999999999997</v>
+      </c>
+      <c r="L137" s="13">
+        <v>25001</v>
+      </c>
+      <c r="M137" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q137" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="R137" s="13">
+        <v>25000</v>
+      </c>
+      <c r="S137" s="13">
+        <v>25000</v>
+      </c>
+      <c r="T137" s="13">
+        <v>25001</v>
+      </c>
+      <c r="U137" s="13">
+        <v>25000</v>
+      </c>
+      <c r="V137" s="13">
+        <v>25000</v>
+      </c>
+      <c r="W137" s="13">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="138" spans="1:23" ht="57.5" x14ac:dyDescent="0.35">
+      <c r="A138" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="B138" s="13">
+        <v>7.4399999999999994E-2</v>
+      </c>
+      <c r="C138" s="13">
+        <v>0.42259999999999998</v>
+      </c>
+      <c r="D138" s="13">
+        <v>0.95209999999999995</v>
+      </c>
+      <c r="E138" s="13">
+        <v>4.7999999999999996E-3</v>
+      </c>
+      <c r="F138" s="13">
+        <v>1.5849</v>
+      </c>
+      <c r="G138" s="13">
+        <v>6.0000000000000002E-5</v>
+      </c>
+      <c r="H138" s="13">
+        <v>2.0000000000000002E-5</v>
+      </c>
+      <c r="I138" s="13">
+        <v>0.44379999999999997</v>
+      </c>
+      <c r="J138" s="13">
+        <v>0.17169999999999999</v>
+      </c>
+      <c r="K138" s="13">
+        <v>0.62829999999999997</v>
+      </c>
+      <c r="L138" s="13">
+        <v>25000</v>
+      </c>
+      <c r="M138" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q138" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="R138" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="S138" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="T138" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="U138" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="V138" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="W138" s="13" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="139" spans="1:23" ht="115" x14ac:dyDescent="0.35">
+      <c r="A139" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="B139" s="13">
+        <v>0.53139999999999998</v>
+      </c>
+      <c r="C139" s="13">
+        <v>0.93189999999999995</v>
+      </c>
+      <c r="D139" s="13">
+        <v>0.82479999999999998</v>
+      </c>
+      <c r="E139" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="F139" s="13">
+        <v>1.5849</v>
+      </c>
+      <c r="G139" s="13">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="H139" s="13">
+        <v>1.1E-4</v>
+      </c>
+      <c r="I139" s="13">
+        <v>8.1900000000000001E-2</v>
+      </c>
+      <c r="J139" s="13">
+        <v>0.52190000000000003</v>
+      </c>
+      <c r="K139" s="13">
+        <v>0.65590000000000004</v>
+      </c>
+      <c r="L139" s="13">
+        <v>25000</v>
+      </c>
+      <c r="M139" s="13" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="140" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="Q140" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="141" spans="1:23" ht="34.5" x14ac:dyDescent="0.35">
+      <c r="Q141" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="R141" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="S141" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="T141" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="U141" s="12" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="142" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A142" s="9"/>
+      <c r="B142" s="9"/>
+      <c r="C142" s="9"/>
+      <c r="D142" s="9"/>
+      <c r="E142" s="9"/>
+      <c r="F142" s="9"/>
+      <c r="G142" s="9"/>
+      <c r="H142" s="9"/>
+      <c r="I142" s="9"/>
+      <c r="Q142" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="R142" s="13">
+        <v>0.2233</v>
+      </c>
+      <c r="S142" s="15">
+        <v>0</v>
+      </c>
+      <c r="T142" s="13">
+        <v>0.46189999999999998</v>
+      </c>
+      <c r="U142" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A143" s="10"/>
+      <c r="B143" s="10"/>
+      <c r="C143" s="10"/>
+      <c r="D143" s="10"/>
+      <c r="E143" s="10"/>
+      <c r="F143" s="11"/>
+      <c r="G143" s="10"/>
+      <c r="H143" s="10"/>
+      <c r="I143" s="10"/>
+      <c r="Q143" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="R143" s="13">
+        <v>0.60909999999999997</v>
+      </c>
+      <c r="S143" s="13">
+        <v>0.27239999999999998</v>
+      </c>
+      <c r="T143" s="13">
+        <v>0.39489999999999997</v>
+      </c>
+      <c r="U143" s="13">
+        <v>0.17130000000000001</v>
+      </c>
+    </row>
+    <row r="144" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A144" s="10"/>
+      <c r="B144" s="10"/>
+      <c r="C144" s="10"/>
+      <c r="D144" s="10"/>
+      <c r="E144" s="10"/>
+      <c r="F144" s="11"/>
+      <c r="G144" s="10"/>
+      <c r="H144" s="10"/>
+      <c r="I144" s="10"/>
+      <c r="Q144" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="R144" s="13">
+        <v>0.95209999999999995</v>
+      </c>
+      <c r="S144" s="13">
+        <v>0.66479999999999995</v>
+      </c>
+      <c r="T144" s="13">
+        <v>0.40560000000000002</v>
+      </c>
+      <c r="U144" s="13">
+        <v>0.30859999999999999</v>
+      </c>
+    </row>
+    <row r="145" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A145" s="10"/>
+      <c r="B145" s="10"/>
+      <c r="C145" s="10"/>
+      <c r="D145" s="10"/>
+      <c r="E145" s="10"/>
+      <c r="F145" s="11"/>
+      <c r="G145" s="10"/>
+      <c r="H145" s="10"/>
+      <c r="I145" s="10"/>
+      <c r="Q145" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="R145" s="13">
+        <v>2.5000000000000001E-3</v>
+      </c>
+      <c r="S145" s="13">
+        <v>8.0000000000000004E-4</v>
+      </c>
+      <c r="T145" s="13">
+        <v>7.9000000000000008E-3</v>
+      </c>
+      <c r="U145" s="13" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="146" spans="1:21" ht="23" x14ac:dyDescent="0.35">
+      <c r="Q146" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="R146" s="13">
+        <v>1.5849</v>
+      </c>
+      <c r="S146" s="13">
+        <v>1.5798000000000001</v>
+      </c>
+      <c r="T146" s="13">
+        <v>1.5849</v>
+      </c>
+      <c r="U146" s="13">
+        <v>1.5789</v>
+      </c>
+    </row>
+    <row r="147" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="Q147" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="R147" s="13">
+        <v>4.0000000000000003E-5</v>
+      </c>
+      <c r="S147" s="13">
+        <v>6.9999999999999994E-5</v>
+      </c>
+      <c r="T147" s="13">
+        <v>6.0000000000000002E-5</v>
+      </c>
+      <c r="U147" s="13">
+        <v>9.0000000000000006E-5</v>
+      </c>
+    </row>
+    <row r="148" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="Q148" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="R148" s="13">
+        <v>4.0000000000000003E-5</v>
+      </c>
+      <c r="S148" s="13">
+        <v>3.0000000000000001E-5</v>
+      </c>
+      <c r="T148" s="13">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="U148" s="13">
+        <v>6.9999999999999994E-5</v>
+      </c>
+    </row>
+    <row r="149" spans="1:21" ht="23" x14ac:dyDescent="0.35">
+      <c r="Q149" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="R149" s="13">
+        <v>0.93540000000000001</v>
+      </c>
+      <c r="S149" s="13">
+        <v>0.7036</v>
+      </c>
+      <c r="T149" s="13">
+        <v>0.52</v>
+      </c>
+      <c r="U149" s="13">
+        <v>0.2238</v>
+      </c>
+    </row>
+    <row r="150" spans="1:21" ht="23" x14ac:dyDescent="0.35">
+      <c r="Q150" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="R150" s="13">
+        <v>0.39290000000000003</v>
+      </c>
+      <c r="S150" s="15">
+        <v>0</v>
+      </c>
+      <c r="T150" s="13">
+        <v>0.89610000000000001</v>
+      </c>
+      <c r="U150" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151" spans="1:21" ht="34.5" x14ac:dyDescent="0.35">
+      <c r="Q151" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="R151" s="13">
+        <v>0.82389999999999997</v>
+      </c>
+      <c r="S151" s="15">
+        <v>0</v>
+      </c>
+      <c r="T151" s="13">
+        <v>0.39450000000000002</v>
+      </c>
+      <c r="U151" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152" spans="1:21" ht="34.5" x14ac:dyDescent="0.35">
+      <c r="Q152" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="R152" s="13">
+        <v>25001</v>
+      </c>
+      <c r="S152" s="13">
+        <v>25002</v>
+      </c>
+      <c r="T152" s="13">
+        <v>25000</v>
+      </c>
+      <c r="U152" s="13">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="153" spans="1:21" ht="23" x14ac:dyDescent="0.35">
+      <c r="Q153" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="R153" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="S153" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="T153" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="U153" s="13" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="156" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="Q156" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="157" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="Q157" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="R157" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="S157" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="T157" s="12" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="158" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="Q158" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="R158" s="13">
+        <v>0.2233</v>
+      </c>
+      <c r="S158" s="13">
+        <v>7.4399999999999994E-2</v>
+      </c>
+      <c r="T158" s="13">
+        <v>0.90180000000000005</v>
+      </c>
+    </row>
+    <row r="159" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="Q159" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="R159" s="13">
+        <v>0.60909999999999997</v>
+      </c>
+      <c r="S159" s="13">
+        <v>0.42259999999999998</v>
+      </c>
+      <c r="T159" s="13">
+        <v>0.26860000000000001</v>
+      </c>
+    </row>
+    <row r="160" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="Q160" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="R160" s="13">
+        <v>0.95209999999999995</v>
+      </c>
+      <c r="S160" s="13">
+        <v>0.95209999999999995</v>
+      </c>
+      <c r="T160" s="13">
+        <v>0.27810000000000001</v>
+      </c>
+    </row>
+    <row r="161" spans="17:20" x14ac:dyDescent="0.35">
+      <c r="Q161" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="R161" s="13">
+        <v>2.5000000000000001E-3</v>
+      </c>
+      <c r="S161" s="13">
+        <v>4.7999999999999996E-3</v>
+      </c>
+      <c r="T161" s="13" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="162" spans="17:20" ht="23" x14ac:dyDescent="0.35">
+      <c r="Q162" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="R162" s="13">
+        <v>1.5849</v>
+      </c>
+      <c r="S162" s="13">
+        <v>1.5849</v>
+      </c>
+      <c r="T162" s="13">
+        <v>1.585</v>
+      </c>
+    </row>
+    <row r="163" spans="17:20" x14ac:dyDescent="0.35">
+      <c r="Q163" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="R163" s="13">
+        <v>4.0000000000000003E-5</v>
+      </c>
+      <c r="S163" s="13">
+        <v>6.0000000000000002E-5</v>
+      </c>
+      <c r="T163" s="13">
+        <v>6.9999999999999994E-5</v>
+      </c>
+    </row>
+    <row r="164" spans="17:20" x14ac:dyDescent="0.35">
+      <c r="Q164" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="R164" s="13">
+        <v>4.0000000000000003E-5</v>
+      </c>
+      <c r="S164" s="13">
+        <v>2.0000000000000002E-5</v>
+      </c>
+      <c r="T164" s="13">
+        <v>4.0000000000000003E-5</v>
+      </c>
+    </row>
+    <row r="165" spans="17:20" ht="23" x14ac:dyDescent="0.35">
+      <c r="Q165" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="R165" s="13">
+        <v>0.93540000000000001</v>
+      </c>
+      <c r="S165" s="13">
+        <v>0.44379999999999997</v>
+      </c>
+      <c r="T165" s="13">
+        <v>0.16539999999999999</v>
+      </c>
+    </row>
+    <row r="166" spans="17:20" ht="23" x14ac:dyDescent="0.35">
+      <c r="Q166" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="R166" s="13">
+        <v>0.39290000000000003</v>
+      </c>
+      <c r="S166" s="13">
+        <v>0.17169999999999999</v>
+      </c>
+      <c r="T166" s="13">
+        <v>0.33639999999999998</v>
+      </c>
+    </row>
+    <row r="167" spans="17:20" ht="34.5" x14ac:dyDescent="0.35">
+      <c r="Q167" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="R167" s="13">
+        <v>0.82389999999999997</v>
+      </c>
+      <c r="S167" s="13">
+        <v>0.62829999999999997</v>
+      </c>
+      <c r="T167" s="13">
+        <v>0.97340000000000004</v>
+      </c>
+    </row>
+    <row r="168" spans="17:20" ht="34.5" x14ac:dyDescent="0.35">
+      <c r="Q168" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="R168" s="13">
+        <v>25001</v>
+      </c>
+      <c r="S168" s="13">
+        <v>25000</v>
+      </c>
+      <c r="T168" s="13">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="169" spans="17:20" x14ac:dyDescent="0.35">
+      <c r="Q169" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="R169" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="S169" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="T169" s="13" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="172" spans="17:20" x14ac:dyDescent="0.35">
+      <c r="Q172" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="173" spans="17:20" ht="23" x14ac:dyDescent="0.35">
+      <c r="Q173" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="R173" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="S173" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="T173" s="12" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="174" spans="17:20" x14ac:dyDescent="0.35">
+      <c r="Q174" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="R174" s="13">
+        <v>0.2233</v>
+      </c>
+      <c r="S174" s="13">
+        <v>7.4399999999999994E-2</v>
+      </c>
+      <c r="T174" s="13">
+        <v>0.53139999999999998</v>
+      </c>
+    </row>
+    <row r="175" spans="17:20" x14ac:dyDescent="0.35">
+      <c r="Q175" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="R175" s="13">
+        <v>0.60909999999999997</v>
+      </c>
+      <c r="S175" s="13">
+        <v>0.42259999999999998</v>
+      </c>
+      <c r="T175" s="13">
+        <v>0.93189999999999995</v>
+      </c>
+    </row>
+    <row r="176" spans="17:20" x14ac:dyDescent="0.35">
+      <c r="Q176" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="R176" s="13">
+        <v>0.95209999999999995</v>
+      </c>
+      <c r="S176" s="13">
+        <v>0.95209999999999995</v>
+      </c>
+      <c r="T176" s="13">
+        <v>0.82479999999999998</v>
+      </c>
+    </row>
+    <row r="177" spans="17:20" x14ac:dyDescent="0.35">
+      <c r="Q177" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="R177" s="13">
+        <v>2.5000000000000001E-3</v>
+      </c>
+      <c r="S177" s="13">
+        <v>4.7999999999999996E-3</v>
+      </c>
+      <c r="T177" s="13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="178" spans="17:20" ht="23" x14ac:dyDescent="0.35">
+      <c r="Q178" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="R178" s="13">
+        <v>1.5849</v>
+      </c>
+      <c r="S178" s="13">
+        <v>1.5849</v>
+      </c>
+      <c r="T178" s="13">
+        <v>1.5849</v>
+      </c>
+    </row>
+    <row r="179" spans="17:20" x14ac:dyDescent="0.35">
+      <c r="Q179" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="R179" s="13">
+        <v>4.0000000000000003E-5</v>
+      </c>
+      <c r="S179" s="13">
+        <v>6.0000000000000002E-5</v>
+      </c>
+      <c r="T179" s="13">
+        <v>1.0000000000000001E-5</v>
+      </c>
+    </row>
+    <row r="180" spans="17:20" x14ac:dyDescent="0.35">
+      <c r="Q180" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="R180" s="13">
+        <v>4.0000000000000003E-5</v>
+      </c>
+      <c r="S180" s="13">
+        <v>2.0000000000000002E-5</v>
+      </c>
+      <c r="T180" s="13">
+        <v>1.1E-4</v>
+      </c>
+    </row>
+    <row r="181" spans="17:20" ht="23" x14ac:dyDescent="0.35">
+      <c r="Q181" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="R181" s="13">
+        <v>0.93540000000000001</v>
+      </c>
+      <c r="S181" s="13">
+        <v>0.44379999999999997</v>
+      </c>
+      <c r="T181" s="13">
+        <v>8.1900000000000001E-2</v>
+      </c>
+    </row>
+    <row r="182" spans="17:20" ht="23" x14ac:dyDescent="0.35">
+      <c r="Q182" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="R182" s="13">
+        <v>0.39290000000000003</v>
+      </c>
+      <c r="S182" s="13">
+        <v>0.17169999999999999</v>
+      </c>
+      <c r="T182" s="13">
+        <v>0.52190000000000003</v>
+      </c>
+    </row>
+    <row r="183" spans="17:20" ht="34.5" x14ac:dyDescent="0.35">
+      <c r="Q183" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="R183" s="13">
+        <v>0.82389999999999997</v>
+      </c>
+      <c r="S183" s="13">
+        <v>0.62829999999999997</v>
+      </c>
+      <c r="T183" s="13">
+        <v>0.65590000000000004</v>
+      </c>
+    </row>
+    <row r="184" spans="17:20" ht="34.5" x14ac:dyDescent="0.35">
+      <c r="Q184" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="R184" s="13">
+        <v>25001</v>
+      </c>
+      <c r="S184" s="13">
+        <v>25000</v>
+      </c>
+      <c r="T184" s="13">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="185" spans="17:20" ht="23" x14ac:dyDescent="0.35">
+      <c r="Q185" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="R185" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="S185" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="T185" s="13" t="s">
+        <v>96</v>
       </c>
     </row>
   </sheetData>
